--- a/report-saved-shipments-summary.xlsx
+++ b/report-saved-shipments-summary.xlsx
@@ -11,15 +11,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
   <si>
     <t>Shipment Report</t>
   </si>
   <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Skyinventories</t>
+  </si>
+  <si>
     <t>Generated At</t>
   </si>
   <si>
-    <t>02 Apr 2026, 09:11</t>
+    <t>02 Apr 2026, 09:24</t>
   </si>
   <si>
     <t>Mode</t>
@@ -529,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -581,74 +587,83 @@
       <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="8"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="5">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1"/>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="8"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="B9" s="5">
+        <v>1</v>
+      </c>
       <c r="C9" s="1"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="8"/>
+    </row>
+    <row r="13" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="8"/>
-    </row>
-    <row r="12" spans="1:3" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="5">
+        <v>1</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="5">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="13">
         <v>1</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="13">
-        <v>1</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>11</v>
+      <c r="C15" s="14" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
